--- a/test_doc/new_org/syllabus_5_science.xlsx
+++ b/test_doc/new_org/syllabus_5_science.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -465,22 +465,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Plants Around Us</t>
+          <t>Changes Around Us</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Parts of a plant</t>
+          <t>Reversible changes</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -491,22 +491,22 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>How seeds travel</t>
+          <t>Irreversible changes</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Components of Food</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sources of water</t>
+          <t>Nutrients</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -521,221 +521,81 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Saving water</t>
+          <t>Balanced diet</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Food and Health</t>
-        </is>
-      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>What we eat</t>
+          <t>Deficiency diseases</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Term 1</t>
-        </is>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Plants Around Us</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Good food habits</t>
+          <t>Parts of a plant</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Term 2</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Shelter</t>
-        </is>
-      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kinds of houses</t>
+          <t>How seeds travel</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Term 1</t>
-        </is>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Animals and shelter</t>
+          <t>Sources of water</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>3</v>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Term 2</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Air Around Us</t>
-        </is>
-      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Air is everywhere</t>
+          <t>Saving water</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Clean and dirty air</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Simple Machines</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Levers and wheels</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>4</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Machines at home</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Earth and Sky</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Day and night</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>The moon and stars</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Materials Around Us</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Solids, liquids, gases</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>4</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Mixing and dissolving</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Keeping Safe</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Safety at home and school</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>3</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>First aid basics</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
